--- a/xls/square_12_tri3_13.xlsx
+++ b/xls/square_12_tri3_13.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -482,13 +482,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>0.12190369942064883</v>
+        <v>0.12190495173770496</v>
       </c>
       <c r="J13">
-        <v>-1.8223436050247412</v>
+        <v>-1.822343614861137</v>
       </c>
       <c r="K13">
-        <v>1.586106859930268</v>
+        <v>1.5861066985324015</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-2.2324480352717018</v>
+        <v>-2.23244864065694</v>
       </c>
       <c r="J14">
-        <v>-1.8109482115134603</v>
+        <v>-1.8109482295315995</v>
       </c>
       <c r="K14">
-        <v>0.7661773303556653</v>
+        <v>0.7661725624744471</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-2.119836157129454</v>
+        <v>-2.119836210080453</v>
       </c>
       <c r="J15">
-        <v>-1.640776948184895</v>
+        <v>-1.6407767601987562</v>
       </c>
       <c r="K15">
-        <v>2.115512126099917</v>
+        <v>2.1155118754545303</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-1.0003494130827473</v>
+        <v>-1.0003492969183494</v>
       </c>
       <c r="J16">
-        <v>-0.8227616364284179</v>
+        <v>-0.8227616299457509</v>
       </c>
       <c r="K16">
-        <v>3.3018570639545652</v>
+        <v>3.301857066608646</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-0.014817320329069234</v>
+        <v>-0.014817320496797732</v>
       </c>
       <c r="J17">
-        <v>-0.020848628521661233</v>
+        <v>-0.020848628636062322</v>
       </c>
       <c r="K17">
-        <v>3.60591716980169</v>
+        <v>3.6059171710339397</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-0.0348198164471497</v>
+        <v>-0.03481981648918523</v>
       </c>
       <c r="J18">
-        <v>-0.028225608275271853</v>
+        <v>-0.02822560831494478</v>
       </c>
       <c r="K18">
-        <v>3.6037155333768713</v>
+        <v>3.6037155341158162</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -692,13 +692,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>0.0007918217706843246</v>
+        <v>0.0007918217622615407</v>
       </c>
       <c r="J19">
-        <v>0.0002255792788248465</v>
+        <v>0.00022557927575274524</v>
       </c>
       <c r="K19">
-        <v>2.7392293308731896</v>
+        <v>2.7392293276519455</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -727,13 +727,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>0.00025939228395561824</v>
+        <v>0.0002593922835752254</v>
       </c>
       <c r="J20">
-        <v>8.649471305737347e-5</v>
+        <v>8.649471292220168e-5</v>
       </c>
       <c r="K20">
-        <v>2.456609004400343</v>
+        <v>2.4566090039555744</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -762,13 +762,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>7.229514350647257e-5</v>
+        <v>7.229514345778215e-5</v>
       </c>
       <c r="J21">
-        <v>1.9841110279651966e-5</v>
+        <v>1.9841110259402017e-5</v>
       </c>
       <c r="K21">
-        <v>2.2617904128710062</v>
+        <v>2.2617904128387836</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -797,13 +797,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>2.7013394954726937e-5</v>
+        <v>2.701339496051254e-5</v>
       </c>
       <c r="J22">
-        <v>-5.592627516181456e-7</v>
+        <v>-5.592627488698088e-7</v>
       </c>
       <c r="K22">
-        <v>2.236236658194594</v>
+        <v>2.2362366584575373</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -832,13 +832,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>1.3402717915002131e-5</v>
+        <v>1.3402717919630762e-5</v>
       </c>
       <c r="J23">
-        <v>-1.1473743208456109e-5</v>
+        <v>-1.1473743205225527e-5</v>
       </c>
       <c r="K23">
-        <v>2.2767236023737416</v>
+        <v>2.2767236026179796</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -867,13 +867,293 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>3.1729032199384415e-5</v>
+        <v>3.172903220960554e-5</v>
       </c>
       <c r="J24">
-        <v>-5.785684975996861e-7</v>
+        <v>-5.785684943691848e-7</v>
       </c>
       <c r="K24">
-        <v>2.2517129611695137</v>
+        <v>2.2517129610397246</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>196</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>676</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25">
+        <v>3750</v>
+      </c>
+      <c r="I25">
+        <v>5.4499985966971046e-5</v>
+      </c>
+      <c r="J25">
+        <v>1.5454055399540334e-5</v>
+      </c>
+      <c r="K25">
+        <v>2.1839492080744343</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>196</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>729</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>4056</v>
+      </c>
+      <c r="I26">
+        <v>-2.1620278049733574e-5</v>
+      </c>
+      <c r="J26">
+        <v>-1.3202010759443204e-5</v>
+      </c>
+      <c r="K26">
+        <v>1.7244869407353856</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>196</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>784</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>4374</v>
+      </c>
+      <c r="I27">
+        <v>-1.1232894926967664e-7</v>
+      </c>
+      <c r="J27">
+        <v>-1.6670141986871653e-7</v>
+      </c>
+      <c r="K27">
+        <v>1.142541069445614</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>196</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>841</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28">
+        <v>4704</v>
+      </c>
+      <c r="I28">
+        <v>-5.083329332558573e-7</v>
+      </c>
+      <c r="J28">
+        <v>-4.277984572905142e-7</v>
+      </c>
+      <c r="K28">
+        <v>1.2129054550356686</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>196</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>900</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29">
+        <v>5046</v>
+      </c>
+      <c r="I29">
+        <v>-3.201580889390983e-7</v>
+      </c>
+      <c r="J29">
+        <v>-2.640870729651674e-7</v>
+      </c>
+      <c r="K29">
+        <v>1.107441264273165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>196</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>169</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>961</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>5400</v>
+      </c>
+      <c r="I30">
+        <v>-2.9352262822748706e-7</v>
+      </c>
+      <c r="J30">
+        <v>-2.527449258721612e-7</v>
+      </c>
+      <c r="K30">
+        <v>1.109174668459385</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>196</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>1024</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31">
+        <v>5766</v>
+      </c>
+      <c r="I31">
+        <v>-2.6919808617019025e-7</v>
+      </c>
+      <c r="J31">
+        <v>-2.3253328330656208e-7</v>
+      </c>
+      <c r="K31">
+        <v>1.0937849807805207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>196</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>1089</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>6144</v>
+      </c>
+      <c r="I32">
+        <v>-2.5354555574636595e-7</v>
+      </c>
+      <c r="J32">
+        <v>-2.19644461650904e-7</v>
+      </c>
+      <c r="K32">
+        <v>1.0824965285674124</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_13.xlsx
+++ b/xls/square_12_tri3_13.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>196</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>169</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>726</v>
+      </c>
+      <c r="I11">
+        <v>5.1635856516937935</v>
+      </c>
+      <c r="J11">
+        <v>1.19459350615221</v>
+      </c>
+      <c r="K11">
+        <v>1.9051520609048742</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>196</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>169</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>169</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>864</v>
+      </c>
+      <c r="I12">
+        <v>3.7753679267269007</v>
+      </c>
+      <c r="J12">
+        <v>0.2205457925828117</v>
+      </c>
+      <c r="K12">
+        <v>1.174067390004529</v>
+      </c>
+    </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>11</v>
